--- a/checklist_forms/050_payment_network_compliance_integration_evaluation_checklist--checklist_forms.xlsx
+++ b/checklist_forms/050_payment_network_compliance_integration_evaluation_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_1</t>
+          <t>payment_network_compliance_integration</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Is the payment network integrated</t>
+          <t>Is the payment network integrated?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_2</t>
+          <t>payment_network_compliance_compliance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Is the payment network fully compliant</t>
+          <t>Is the payment network fully compliant?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_3</t>
+          <t>payment_network_security</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Is the payment network fully integrated</t>
+          <t>Is the payment network secure?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_4</t>
+          <t>payment_network_update_protocol</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Is the payment network compliant</t>
+          <t>Is the payment network up-to-date with the latest security protocols?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_5</t>
+          <t>payment_network_compliance_standards</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Is the payment network integrated</t>
+          <t>Does the payment network meet the required compliance standards?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_6</t>
+          <t>payment_network_activity_monitoring</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Is the payment network secure</t>
+          <t>Is there a clear process for monitoring payment network activity?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_7</t>
+          <t>payment_network_testing_and_validation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Is the payment network integrated</t>
+          <t>Is the payment network properly tested and validated?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_8</t>
+          <t>payment_network_error_handling</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Is the payment network compliant</t>
+          <t>Is there a process for handling payment network errors and failures?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_9</t>
+          <t>payment_network_integration_main_system</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Is the payment network secure</t>
+          <t>Is the payment network integrated with the main system?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_10</t>
+          <t>payment_network_reporting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Is the payment network integrated</t>
+          <t>Is there a process for reporting and addressing payment network issues?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_11</t>
+          <t>payment_network_documentation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Is the payment network compliant</t>
+          <t>Is the payment network properly documented and maintained?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_12</t>
+          <t>payment_network_update_software_hardware</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Is the payment network secure</t>
+          <t>Is there a clear process for updating payment network software and hardware?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_13</t>
+          <t>payment_network_update_protocol_implementation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Is the payment network integrated</t>
+          <t>Payment Network Update Protocol Implementation</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_14</t>
+          <t>payment_network_compliance_reporting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Is the payment network compliant</t>
+          <t>Payment Network Compliance Reporting</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_15</t>
+          <t>payment_network_main_system_interface</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Is the payment network secure</t>
+          <t>How does the payment network interface with the main system?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_16</t>
+          <t>payment_network_main_system_interface_type</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Is the payment network integrated</t>
+          <t>Payment Network Main System Interface Type</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_17</t>
+          <t>payment_network_update_protocol_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Is the payment network compliant</t>
+          <t>Payment Network Update Protocol</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_18</t>
+          <t>payment_network_compliance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Is the payment network secure</t>
+          <t>Payment Network Compliance</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Is the payment network integrated</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Is the payment network compliant</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Is the payment network secure</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Is the payment network integrated</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Is the payment network compliant</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Is the payment network secure</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Is the payment network integrated</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,7 +965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_1_choices</t>
+          <t>payment_network_compliance_integration_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +982,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_1_choices</t>
+          <t>payment_network_compliance_integration_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +999,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_2_choices</t>
+          <t>payment_network_compliance_compliance_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1016,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_2_choices</t>
+          <t>payment_network_compliance_compliance_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +1033,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_4_choices</t>
+          <t>payment_network_security_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1050,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_4_choices</t>
+          <t>payment_network_security_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,41 +1067,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_5_choices</t>
+          <t>payment_network_update_protocol_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_5_choices</t>
+          <t>payment_network_update_protocol_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_6_choices</t>
+          <t>payment_network_compliance_standards_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1118,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_6_choices</t>
+          <t>payment_network_compliance_standards_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,41 +1135,41 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_7_choices</t>
+          <t>payment_network_activity_monitoring_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_7_choices</t>
+          <t>payment_network_activity_monitoring_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_9_choices</t>
+          <t>payment_network_testing_and_validation_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1186,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_9_choices</t>
+          <t>payment_network_testing_and_validation_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,41 +1203,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_10_choices</t>
+          <t>payment_network_error_handling_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_10_choices</t>
+          <t>payment_network_error_handling_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_11_choices</t>
+          <t>payment_network_integration_main_system_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_11_choices</t>
+          <t>payment_network_integration_main_system_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1271,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_12_choices</t>
+          <t>payment_network_reporting_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1288,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_12_choices</t>
+          <t>payment_network_reporting_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,41 +1305,41 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_13_choices</t>
+          <t>payment_network_documentation_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_13_choices</t>
+          <t>payment_network_documentation_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_15_choices</t>
+          <t>payment_network_update_software_hardware_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1356,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_15_choices</t>
+          <t>payment_network_update_software_hardware_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,41 +1373,41 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_16_choices</t>
+          <t>payment_network_update_protocol_implementation_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>implemented</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_16_choices</t>
+          <t>payment_network_update_protocol_implementation_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>not_implemented</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Not Implemented</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_17_choices</t>
+          <t>payment_network_compliance_reporting_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1424,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_17_choices</t>
+          <t>payment_network_compliance_reporting_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1602,238 +1441,136 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_18_choices</t>
+          <t>payment_network_main_system_interface_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>api</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>API</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_18_choices</t>
+          <t>payment_network_main_system_interface_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>websocket</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Websocket</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_19_choices</t>
+          <t>payment_network_main_system_interface_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_19_choices</t>
+          <t>payment_network_main_system_interface_type_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>api</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>API</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_21_choices</t>
+          <t>payment_network_main_system_interface_type_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>websocket</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Websocket</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_21_choices</t>
+          <t>payment_network_main_system_interface_type_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_22_choices</t>
+          <t>payment_network_compliance_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_22_choices</t>
+          <t>payment_network_compliance_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_23_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_23_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
           <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_24_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_24_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_25_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>payment_network_compliance_integration_evaluation_checklist_25_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Fair</t>
         </is>
       </c>
     </row>
